--- a/src/assets/中油匯出.xlsx
+++ b/src/assets/中油匯出.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,6 +67,22 @@
   </si>
   <si>
     <t>油量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>負責業務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考金額</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>折讓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>售價</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -138,7 +154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -153,6 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
@@ -448,10 +467,14 @@
     <col min="9" max="9" width="32.25" style="4" customWidth="1"/>
     <col min="10" max="10" width="13.75" style="4" customWidth="1"/>
     <col min="11" max="11" width="20.75" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="4"/>
+    <col min="12" max="12" width="20.75" style="5" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="4" customWidth="1"/>
+    <col min="14" max="14" width="20.75" style="5" customWidth="1"/>
+    <col min="15" max="15" width="16.125" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5">
+    <row r="1" spans="1:15" ht="16.5">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -484,6 +507,18 @@
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/中油匯出.xlsx
+++ b/src/assets/中油匯出.xlsx
@@ -90,6 +90,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="#,##0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="12"/>
@@ -154,7 +159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -171,6 +176,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,10 +488,10 @@
     <col min="7" max="7" width="25.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="53" style="4" customWidth="1"/>
     <col min="9" max="9" width="32.25" style="4" customWidth="1"/>
-    <col min="10" max="10" width="13.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="20.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="7" customWidth="1"/>
+    <col min="11" max="11" width="20.75" style="9" customWidth="1"/>
     <col min="12" max="12" width="20.75" style="5" customWidth="1"/>
-    <col min="13" max="13" width="20.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="20.75" style="11" customWidth="1"/>
     <col min="14" max="14" width="20.75" style="5" customWidth="1"/>
     <col min="15" max="15" width="16.125" style="4" customWidth="1"/>
     <col min="16" max="16384" width="9" style="4"/>
@@ -502,16 +525,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="10" t="s">
         <v>13</v>
       </c>
       <c r="N1" s="3" t="s">

--- a/src/assets/中油匯出.xlsx
+++ b/src/assets/中油匯出.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>客戶名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t>售價</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中油檔案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -476,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16.625" style="1" customWidth="1"/>
@@ -494,10 +498,11 @@
     <col min="13" max="13" width="20.75" style="11" customWidth="1"/>
     <col min="14" max="14" width="20.75" style="5" customWidth="1"/>
     <col min="15" max="15" width="16.125" style="4" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="4"/>
+    <col min="16" max="16" width="41.75" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.5">
+    <row r="1" spans="1:16" ht="16.5">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -542,6 +547,9 @@
       </c>
       <c r="O1" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
